--- a/rabbit-web-app/public/sample_excels/driver_single_sample.xlsx
+++ b/rabbit-web-app/public/sample_excels/driver_single_sample.xlsx
@@ -398,31 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W2"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="23.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-    <col min="16" max="16" width="17.83203125" customWidth="1"/>
-    <col min="17" max="17" width="16.83203125" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" customWidth="1"/>
-    <col min="19" max="19" width="31.83203125" customWidth="1"/>
-    <col min="20" max="20" width="19.83203125" customWidth="1"/>
-    <col min="21" max="21" width="19.83203125" customWidth="1"/>
-    <col min="22" max="22" width="42.83203125" customWidth="1"/>
-    <col min="23" max="23" width="37.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -459,7 +434,7 @@
         <v>Country*</v>
       </c>
       <c r="L1" t="str">
-        <v>Postal Code</v>
+        <v>Zip Code</v>
       </c>
       <c r="M1" t="str">
         <v>License Number</v>
@@ -503,7 +478,7 @@
         <v>gurpreet.singh.driver@gmail.com</v>
       </c>
       <c r="C2" t="str">
-        <v>+1 555-234-8891</v>
+        <v>555-234-8891</v>
       </c>
       <c r="D2" t="str">
         <v>ACHA9999</v>
@@ -554,7 +529,7 @@
         <v>gurpreet.personal@gmail.com</v>
       </c>
       <c r="T2" t="str">
-        <v>+1 555-234-8890</v>
+        <v>555-234-8890</v>
       </c>
       <c r="U2" t="str">
         <v>View, Edit, Add</v>
